--- a/data/dividends_info_20260820.xlsx
+++ b/data/dividends_info_20260820.xlsx
@@ -522,12 +522,8 @@
           <t>NL0000226223</t>
         </is>
       </c>
-      <c r="H2" t="n">
-        <v>43.86000061035156</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.205198355557612</v>
-      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
         <v>207</v>
       </c>
@@ -570,10 +566,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>69.05000305175781</v>
+        <v>68.19999694824219</v>
       </c>
       <c r="I3" t="n">
-        <v>1.013758101466413</v>
+        <v>1.026393007805028</v>
       </c>
       <c r="J3" t="n">
         <v>186</v>
@@ -617,10 +613,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9.319999694824219</v>
+        <v>9.140000343322754</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6437768451142812</v>
+        <v>0.6564551175737441</v>
       </c>
       <c r="J4" t="n">
         <v>116</v>
@@ -710,12 +706,8 @@
           <t>NL0000226223</t>
         </is>
       </c>
-      <c r="H6" t="n">
-        <v>43.86000061035156</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.205198355557612</v>
-      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
         <v>116</v>
       </c>
@@ -805,10 +797,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>23.97500038146973</v>
+        <v>24.54999923706055</v>
       </c>
       <c r="I8" t="n">
-        <v>1.126173079057312</v>
+        <v>1.099796368190552</v>
       </c>
       <c r="J8" t="n">
         <v>95</v>
@@ -852,10 +844,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>22.78000068664551</v>
+        <v>22.93000030517578</v>
       </c>
       <c r="I9" t="n">
-        <v>2.589991142300009</v>
+        <v>2.573048373954119</v>
       </c>
       <c r="J9" t="n">
         <v>95</v>
@@ -899,10 +891,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5.760000228881836</v>
+        <v>5.809999942779541</v>
       </c>
       <c r="I10" t="n">
-        <v>3.472222084248513</v>
+        <v>3.442340825640675</v>
       </c>
       <c r="J10" t="n">
         <v>88</v>
@@ -946,10 +938,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>10.27999973297119</v>
+        <v>10.43000030517578</v>
       </c>
       <c r="I11" t="n">
-        <v>4.474708287439301</v>
+        <v>4.410354616880785</v>
       </c>
       <c r="J11" t="n">
         <v>67</v>
@@ -993,10 +985,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>7.650000095367432</v>
+        <v>7.599999904632568</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7843137157126817</v>
+        <v>0.7894736941171157</v>
       </c>
       <c r="J12" t="n">
         <v>60</v>
@@ -1040,10 +1032,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.4699999988079071</v>
+        <v>0.4779999852180481</v>
       </c>
       <c r="I13" t="n">
-        <v>0.851063831945845</v>
+        <v>0.8368201095603234</v>
       </c>
       <c r="J13" t="n">
         <v>60</v>
@@ -1134,10 +1126,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>5.039999961853027</v>
+        <v>4.989999771118164</v>
       </c>
       <c r="I15" t="n">
-        <v>0.753968259674922</v>
+        <v>0.7615230810218038</v>
       </c>
       <c r="J15" t="n">
         <v>39</v>
@@ -1181,10 +1173,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>23.97500038146973</v>
+        <v>24.54999923706055</v>
       </c>
       <c r="I16" t="n">
-        <v>1.126173079057312</v>
+        <v>1.099796368190552</v>
       </c>
       <c r="J16" t="n">
         <v>32</v>
@@ -1228,10 +1220,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>2.003999948501587</v>
+        <v>2.01200008392334</v>
       </c>
       <c r="I17" t="n">
-        <v>2.844311450338087</v>
+        <v>2.833001869903092</v>
       </c>
       <c r="J17" t="n">
         <v>32</v>
@@ -1274,12 +1266,8 @@
           <t>NL0000226223</t>
         </is>
       </c>
-      <c r="H18" t="n">
-        <v>43.86000061035156</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0.205198355557612</v>
-      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
         <v>32</v>
       </c>
@@ -1322,10 +1310,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>89.94999694824219</v>
+        <v>89.80000305175781</v>
       </c>
       <c r="I19" t="n">
-        <v>1.478599271954718</v>
+        <v>1.481068991983699</v>
       </c>
       <c r="J19" t="n">
         <v>32</v>
@@ -1416,10 +1404,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0.4699999988079071</v>
+        <v>0.4779999852180481</v>
       </c>
       <c r="I21" t="n">
-        <v>0.851063831945845</v>
+        <v>0.8368201095603234</v>
       </c>
       <c r="J21" t="n">
         <v>4</v>
@@ -1510,10 +1498,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>5.039999961853027</v>
+        <v>4.989999771118164</v>
       </c>
       <c r="I23" t="n">
-        <v>0.753968259674922</v>
+        <v>0.7615230810218038</v>
       </c>
       <c r="J23" t="n">
         <v>-17</v>
@@ -1604,10 +1592,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>2.490000009536743</v>
+        <v>2.529999971389771</v>
       </c>
       <c r="I25" t="n">
-        <v>5.942530097721934</v>
+        <v>5.848577141236812</v>
       </c>
       <c r="J25" t="n">
         <v>-17</v>
@@ -1651,10 +1639,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>5.980000019073486</v>
+        <v>5.96999979019165</v>
       </c>
       <c r="I26" t="n">
-        <v>4.18060199335474</v>
+        <v>4.187604837285504</v>
       </c>
       <c r="J26" t="n">
         <v>-24</v>
